--- a/education_forms/034_school_to_work_pathways_workshop_registration_form--education_forms.xlsx
+++ b/education_forms/034_school_to_work_pathways_workshop_registration_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'grade_1'}</t>
+          <t>grade_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 1'}</t>
+          <t>Grade 1</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'grade_2'}</t>
+          <t>grade_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 2'}</t>
+          <t>Grade 2</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'grade_3'}</t>
+          <t>grade_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 3'}</t>
+          <t>Grade 3</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'grade_4'}</t>
+          <t>grade_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 4'}</t>
+          <t>Grade 4</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'grade_5'}</t>
+          <t>grade_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 5'}</t>
+          <t>Grade 5</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'grade_6'}</t>
+          <t>grade_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 6'}</t>
+          <t>Grade 6</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'grade_7'}</t>
+          <t>grade_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 7'}</t>
+          <t>Grade 7</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'grade_8'}</t>
+          <t>grade_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 8'}</t>
+          <t>Grade 8</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'grade_9'}</t>
+          <t>grade_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 9'}</t>
+          <t>Grade 9</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'grade_10'}</t>
+          <t>grade_10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Grade 10'}</t>
+          <t>Grade 10</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'teacher_1'}</t>
+          <t>teacher_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Teacher 1'}</t>
+          <t>Teacher 1</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'teacher_2'}</t>
+          <t>teacher_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Teacher 2'}</t>
+          <t>Teacher 2</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'teacher_3'}</t>
+          <t>teacher_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Teacher 3'}</t>
+          <t>Teacher 3</t>
         </is>
       </c>
     </row>
